--- a/outputs/Block5_Election_Snapshot.xlsx
+++ b/outputs/Block5_Election_Snapshot.xlsx
@@ -58,16 +58,16 @@
     <t>Overall Diagnostic Stability</t>
   </si>
   <si>
-    <t>52.07%</t>
-  </si>
-  <si>
-    <t>45.01%</t>
+    <t>52.36%</t>
+  </si>
+  <si>
+    <t>44.72%</t>
   </si>
   <si>
     <t>2.92%</t>
   </si>
   <si>
-    <t>D 219 - R 216</t>
+    <t>D 223 - R 212</t>
   </si>
   <si>
     <t>Democratic</t>
@@ -79,7 +79,7 @@
     <t>Republican</t>
   </si>
   <si>
-    <t>70.0/100</t>
+    <t>69.1/100</t>
   </si>
 </sst>
 </file>
@@ -493,7 +493,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -501,7 +501,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2">

--- a/outputs/Block5_Election_Snapshot.xlsx
+++ b/outputs/Block5_Election_Snapshot.xlsx
@@ -67,7 +67,7 @@
     <t>2.92%</t>
   </si>
   <si>
-    <t>D 223 - R 212</t>
+    <t>D 227 - R 208</t>
   </si>
   <si>
     <t>Democratic</t>
@@ -79,7 +79,7 @@
     <t>Republican</t>
   </si>
   <si>
-    <t>69.1/100</t>
+    <t>78.0/100</t>
   </si>
 </sst>
 </file>
@@ -493,7 +493,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -501,7 +501,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2">

--- a/outputs/Block5_Election_Snapshot.xlsx
+++ b/outputs/Block5_Election_Snapshot.xlsx
@@ -1,111 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FinalSnapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RunMetadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExportProvenance" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Projection</t>
-  </si>
-  <si>
-    <t>Democratic Popular Vote</t>
-  </si>
-  <si>
-    <t>Republican Popular Vote</t>
-  </si>
-  <si>
-    <t>Other Popular Vote</t>
-  </si>
-  <si>
-    <t>House Projection</t>
-  </si>
-  <si>
-    <t>House Control</t>
-  </si>
-  <si>
-    <t>House Margin</t>
-  </si>
-  <si>
-    <t>House Democratic Net Change</t>
-  </si>
-  <si>
-    <t>Senate Projection</t>
-  </si>
-  <si>
-    <t>Senate Control</t>
-  </si>
-  <si>
-    <t>Senate Margin</t>
-  </si>
-  <si>
-    <t>Senate Democratic Net Change</t>
-  </si>
-  <si>
-    <t>Overall Diagnostic Stability</t>
-  </si>
-  <si>
-    <t>52.36%</t>
-  </si>
-  <si>
-    <t>44.72%</t>
-  </si>
-  <si>
-    <t>2.92%</t>
-  </si>
-  <si>
-    <t>D 227 - R 208</t>
-  </si>
-  <si>
-    <t>Democratic</t>
-  </si>
-  <si>
-    <t>D 50 - R 50</t>
-  </si>
-  <si>
-    <t>Republican</t>
-  </si>
-  <si>
-    <t>78.0/100</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -120,35 +48,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -436,115 +422,609 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Popular vote D (%)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>52.9566065934066</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Popular vote R (%)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>44.1233934065934</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Popular vote Other (%)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>House status</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pending Block 5C race-first</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senate status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pending Block 5B race-first</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Run ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-dd0af9f21104-20261020T060932Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Source File</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>/Users/juani/Documents/GitHub/midterms-2026-forecast/Model.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Source SHA-256</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>dd0af9f211044926f193d3ea436dabde2b2960f060ab768c53232e3e59f37c10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Source Modified UTC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-20T02:41:23.457320+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Run Started UTC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-10-20T06:09:32.147340+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report Generated UTC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-10-20T06:11:56.240312+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Historical Years</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2006, 2010, 2014, 2018, 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Feature Count</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P Target Count</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Monte Carlo Simulations</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Model Version</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>v30 STABLE · v28 House incumbent preserved + 35-race Senate engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>National Validation</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Five outer historical tests with strict inner LOEO isolation; v30 national contract evaluated per test</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Popular Vote Validation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Margin-first nested competition: expectation anchor, guarded error correction, Ridge, trees and historical mean</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Module Isolation</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>One-way frozen national signal contract; counterfactual and exact-mutation tests</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senate Validation</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Strictly nested alpha, weights and calibration by election cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>National Complexity Tolerance</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senate Baseline Safeguard</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Polling-error correction retained — inner LOEO improved MAE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Input Unit Contract</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Economic batteries normalized to proportions; net favorability recomputed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Diagnostic Stability Definition</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sensitivity to TreeEnsemble and constraint engine; heuristic, not accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Validation Limitation</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Five completed midterm cycles; 210 target comparisons are repeated measures, not 210 independent elections; source-derived identities reconciled in InputReconciliation</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>House v28 Architecture</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>House fundamentals + ratings + observed polling/nowcast; component weights validation-aware and polling coverage-aware</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>House Automatic Sources</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Exactly 2 APIs (Inside Elections, VoteHub) + 1 automatic CSV (Split Ticket); hard stop, no fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>House Historical Universe</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2006 / 2010 / 2014 / 2018 / 2022 comparable midterms only</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>House covariance validation</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>STRICT NESTED LOEO: outer election absent from every inner point fit and covariance selection</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Legacy aggregate rating predictor policy</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Retired from national, Senate-state, and generated Scenario-runtime predictors</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>House historical aggregate policy</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>House compatibility rating/result buckets rebuilt from identified district rows; structural missingness remains explicit</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>v30 Popular Vote Policy</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Inherited v28 ExpectedVoteAnchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>v30 House Production Engine</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Block 5C race-first House incumbent</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>v30 Senate Architecture</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>35-race structural motor + polling enrichment on 12 monitored races</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>v30 Senate Structural Gate</t>
+        </is>
+      </c>
+      <c r="B31" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>v30 Monitored Method</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>POLL_5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>v30 Senate Promotion</t>
+        </is>
+      </c>
+      <c r="B33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>v30 Senate Modeled Races</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>v30 HTML Policy</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Public Senate map highlights 12 monitored races and uses numeric margins for all 35 when v30 is promoted</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Run ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-dd0af9f21104-20261020T060932Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Final Report</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Election_Model_Final_Report_v30.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Final Report SHA256</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>6254f3f54af6754b67deae4c4b8445dd2c4a92fbbcded33cef106f4df9255f2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Generated UTC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-20T06:12:00.987520+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Input contract</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Consolidated Final Report from this run; no archived inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Metric clarification</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Current v30 diagnostic/reporting view</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/Block5_Election_Snapshot.xlsx
+++ b/outputs/Block5_Election_Snapshot.xlsx
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.9566065934066</v>
+        <v>52.80457815565729</v>
       </c>
       <c r="C2" t="inlineStr"/>
     </row>
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.1233934065934</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="C3" t="inlineStr"/>
     </row>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.92</v>
+        <v>2.919999999999995</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,7 +540,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-dd0af9f21104-20261020T060932Z</t>
+          <t>2026-69084551907b-20261024T072445Z</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dd0af9f211044926f193d3ea436dabde2b2960f060ab768c53232e3e59f37c10</t>
+          <t>69084551907b520052181adf33e09563f086f0b6de4f1d95d2e192b06c14159d</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T02:41:23.457320+00:00</t>
+          <t>2026-10-24T07:22:07.989106+00:00</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20T06:09:32.147340+00:00</t>
+          <t>2026-10-24T07:24:45.840036+00:00</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20T06:11:56.240312+00:00</t>
+          <t>2026-10-24T07:26:59.123079+00:00</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>35-race structural motor + polling enrichment on 12 monitored races</t>
+          <t>35-race structural motor + polling enrichment on 15 monitored races</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,53 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Public Senate map highlights 12 monitored races and uses numeric margins for all 35 when v30 is promoted</t>
+          <t>Public Senate map highlights 15 monitored races and uses numeric margins for all 35 when v30 is promoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration source</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Recovered Model(5).xlsx / Senate Historic</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration rows</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration reference SHA256</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>7b3f807a5128485c7fd4de43f99733784af9627e835db4777c047b68e762feb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senate production policy</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Recovered 5B calibration + 15 current monitored races; automatic structural blending disabled</t>
         </is>
       </c>
     </row>
@@ -960,7 +1006,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-dd0af9f21104-20261020T060932Z</t>
+          <t>2026-69084551907b-20261024T072445Z</t>
         </is>
       </c>
     </row>
@@ -984,7 +1030,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6254f3f54af6754b67deae4c4b8445dd2c4a92fbbcded33cef106f4df9255f2a</t>
+          <t>8a7bfde9efafe267b78417530287877a5e160939951e8ae39d62138f60d4e05a</t>
         </is>
       </c>
     </row>
@@ -996,7 +1042,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T06:12:00.987520+00:00</t>
+          <t>2026-10-24T07:27:04.098692+00:00</t>
         </is>
       </c>
     </row>
